--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>286000</v>
+        <v>283500</v>
       </c>
       <c r="C419" t="n">
-        <v>149230</v>
+        <v>300923</v>
       </c>
       <c r="D419" t="n">
-        <v>298108</v>
+        <v>297972</v>
       </c>
       <c r="E419" t="n">
-        <v>301717</v>
+        <v>301389</v>
       </c>
       <c r="F419" t="n">
-        <v>288349</v>
+        <v>287624</v>
       </c>
       <c r="G419" t="n">
-        <v>296058</v>
+        <v>295662</v>
       </c>
       <c r="H419" t="n">
-        <v>0.8991102871841583</v>
+        <v>0.8965700833263841</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>0.8965700833263841</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>291000</v>
+      </c>
+      <c r="C420" t="n">
+        <v>487505</v>
+      </c>
+      <c r="D420" t="n">
+        <v>297046</v>
+      </c>
+      <c r="E420" t="n">
+        <v>299098</v>
+      </c>
+      <c r="F420" t="n">
+        <v>285815</v>
+      </c>
+      <c r="G420" t="n">
+        <v>293986</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0.885819119524289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>295000</v>
+        <v>291000</v>
       </c>
       <c r="C421" t="n">
-        <v>35324</v>
+        <v>215315</v>
       </c>
       <c r="D421" t="n">
-        <v>296599</v>
+        <v>296536</v>
       </c>
       <c r="E421" t="n">
-        <v>299080</v>
+        <v>298885</v>
       </c>
       <c r="F421" t="n">
-        <v>286145</v>
+        <v>286643</v>
       </c>
       <c r="G421" t="n">
-        <v>293942</v>
+        <v>294021</v>
       </c>
       <c r="H421" t="n">
-        <v>0.8855368746512031</v>
+        <v>0.8860436324915166</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>0.8860436324915166</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>294500</v>
+      </c>
+      <c r="C422" t="n">
+        <v>221230</v>
+      </c>
+      <c r="D422" t="n">
+        <v>295836</v>
+      </c>
+      <c r="E422" t="n">
+        <v>298769</v>
+      </c>
+      <c r="F422" t="n">
+        <v>288409</v>
+      </c>
+      <c r="G422" t="n">
+        <v>294338</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0.8880770785089773</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>0.8880770785089773</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>296000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>360064</v>
+      </c>
+      <c r="D423" t="n">
+        <v>295642</v>
+      </c>
+      <c r="E423" t="n">
+        <v>298181</v>
+      </c>
+      <c r="F423" t="n">
+        <v>291200</v>
+      </c>
+      <c r="G423" t="n">
+        <v>295008</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.8923748981673327</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>0.8923748981673327</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>290500</v>
+      </c>
+      <c r="C424" t="n">
+        <v>181136</v>
+      </c>
+      <c r="D424" t="n">
+        <v>296615</v>
+      </c>
+      <c r="E424" t="n">
+        <v>297957</v>
+      </c>
+      <c r="F424" t="n">
+        <v>292695</v>
+      </c>
+      <c r="G424" t="n">
+        <v>295756</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.8971730610097952</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>0.8971730610097952</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>282000</v>
+      </c>
+      <c r="C425" t="n">
+        <v>263175</v>
+      </c>
+      <c r="D425" t="n">
+        <v>297105</v>
+      </c>
+      <c r="E425" t="n">
+        <v>296674</v>
+      </c>
+      <c r="F425" t="n">
+        <v>291093</v>
+      </c>
+      <c r="G425" t="n">
+        <v>294957</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.8920477507008011</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>0.8920477507008011</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>284000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>172874</v>
+      </c>
+      <c r="D426" t="n">
+        <v>296966</v>
+      </c>
+      <c r="E426" t="n">
+        <v>295636</v>
+      </c>
+      <c r="F426" t="n">
+        <v>290087</v>
+      </c>
+      <c r="G426" t="n">
+        <v>294230</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.8873842956386753</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>289000</v>
+      </c>
+      <c r="C427" t="n">
+        <v>181005</v>
+      </c>
+      <c r="D427" t="n">
+        <v>296879</v>
+      </c>
+      <c r="E427" t="n">
+        <v>295505</v>
+      </c>
+      <c r="F427" t="n">
+        <v>289074</v>
+      </c>
+      <c r="G427" t="n">
+        <v>293819</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.8847478719378035</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>0.8847478719378035</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>285000</v>
+      </c>
+      <c r="C428" t="n">
+        <v>234275</v>
+      </c>
+      <c r="D428" t="n">
+        <v>298121</v>
+      </c>
+      <c r="E428" t="n">
+        <v>294440</v>
+      </c>
+      <c r="F428" t="n">
+        <v>285734</v>
+      </c>
+      <c r="G428" t="n">
+        <v>292765</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.8779868242961519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>0.8779868242961519</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>281000</v>
+      </c>
+      <c r="C429" t="n">
+        <v>167526</v>
+      </c>
+      <c r="D429" t="n">
+        <v>298539</v>
+      </c>
+      <c r="E429" t="n">
+        <v>293159</v>
+      </c>
+      <c r="F429" t="n">
+        <v>284108</v>
+      </c>
+      <c r="G429" t="n">
+        <v>291935</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.8726626596447564</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>0.8726626596447564</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>269000</v>
+      </c>
+      <c r="C430" t="n">
+        <v>331460</v>
+      </c>
+      <c r="D430" t="n">
+        <v>297880</v>
+      </c>
+      <c r="E430" t="n">
+        <v>290938</v>
+      </c>
+      <c r="F430" t="n">
+        <v>280012</v>
+      </c>
+      <c r="G430" t="n">
+        <v>289610</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.8577485839646424</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>0.8577485839646424</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>267500</v>
+      </c>
+      <c r="C431" t="n">
+        <v>297073</v>
+      </c>
+      <c r="D431" t="n">
+        <v>297692</v>
+      </c>
+      <c r="E431" t="n">
+        <v>285835</v>
+      </c>
+      <c r="F431" t="n">
+        <v>276375</v>
+      </c>
+      <c r="G431" t="n">
+        <v>286634</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.8386585670940967</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>0.8386585670940967</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>256000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>297131</v>
+      </c>
+      <c r="D432" t="n">
+        <v>297050</v>
+      </c>
+      <c r="E432" t="n">
+        <v>284041</v>
+      </c>
+      <c r="F432" t="n">
+        <v>270093</v>
+      </c>
+      <c r="G432" t="n">
+        <v>283728</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.8200175761580057</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>0.8200175761580057</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>246500</v>
+      </c>
+      <c r="C433" t="n">
+        <v>298593</v>
+      </c>
+      <c r="D433" t="n">
+        <v>295843</v>
+      </c>
+      <c r="E433" t="n">
+        <v>280444</v>
+      </c>
+      <c r="F433" t="n">
+        <v>262522</v>
+      </c>
+      <c r="G433" t="n">
+        <v>279603</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.7935571193061908</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>0.7935571193061908</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>228000</v>
+      </c>
+      <c r="C434" t="n">
+        <v>465018</v>
+      </c>
+      <c r="D434" t="n">
+        <v>293628</v>
+      </c>
+      <c r="E434" t="n">
+        <v>275179</v>
+      </c>
+      <c r="F434" t="n">
+        <v>251186</v>
+      </c>
+      <c r="G434" t="n">
+        <v>273331</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.753324395579019</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>0.753324395579019</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>238500</v>
+      </c>
+      <c r="C435" t="n">
+        <v>381130</v>
+      </c>
+      <c r="D435" t="n">
+        <v>292192</v>
+      </c>
+      <c r="E435" t="n">
+        <v>272002</v>
+      </c>
+      <c r="F435" t="n">
+        <v>245010</v>
+      </c>
+      <c r="G435" t="n">
+        <v>269735</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.7302572918604426</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>0.7302572918604426</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>244500</v>
+      </c>
+      <c r="C436" t="n">
+        <v>294658</v>
+      </c>
+      <c r="D436" t="n">
+        <v>291094</v>
+      </c>
+      <c r="E436" t="n">
+        <v>269243</v>
+      </c>
+      <c r="F436" t="n">
+        <v>241076</v>
+      </c>
+      <c r="G436" t="n">
+        <v>267138</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.7135984296921607</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>0.7135984296921607</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>237000</v>
+      </c>
+      <c r="C437" t="n">
+        <v>225187</v>
+      </c>
+      <c r="D437" t="n">
+        <v>289944</v>
+      </c>
+      <c r="E437" t="n">
+        <v>267812</v>
+      </c>
+      <c r="F437" t="n">
+        <v>237861</v>
+      </c>
+      <c r="G437" t="n">
+        <v>265206</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.7012053139012016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>0.7012053139012016</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>245000</v>
+      </c>
+      <c r="C438" t="n">
+        <v>208117</v>
+      </c>
+      <c r="D438" t="n">
+        <v>286070</v>
+      </c>
+      <c r="E438" t="n">
+        <v>264464</v>
+      </c>
+      <c r="F438" t="n">
+        <v>237166</v>
+      </c>
+      <c r="G438" t="n">
+        <v>262567</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.6842770361722463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>0.6842770361722463</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>241500</v>
+      </c>
+      <c r="C439" t="n">
+        <v>190930</v>
+      </c>
+      <c r="D439" t="n">
+        <v>285412</v>
+      </c>
+      <c r="E439" t="n">
+        <v>262347</v>
+      </c>
+      <c r="F439" t="n">
+        <v>241081</v>
+      </c>
+      <c r="G439" t="n">
+        <v>262947</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.6867146055307165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>0.6867146055307165</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>245000</v>
+      </c>
+      <c r="C440" t="n">
+        <v>190551</v>
+      </c>
+      <c r="D440" t="n">
+        <v>284825</v>
+      </c>
+      <c r="E440" t="n">
+        <v>260149</v>
+      </c>
+      <c r="F440" t="n">
+        <v>242641</v>
+      </c>
+      <c r="G440" t="n">
+        <v>262539</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.6840974257984642</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>0.6840974257984642</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>246500</v>
+      </c>
+      <c r="C441" t="n">
+        <v>218814</v>
+      </c>
+      <c r="D441" t="n">
+        <v>281661</v>
+      </c>
+      <c r="E441" t="n">
+        <v>259547</v>
+      </c>
+      <c r="F441" t="n">
+        <v>242928</v>
+      </c>
+      <c r="G441" t="n">
+        <v>261379</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.6766564245989237</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>0.6766564245989237</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>255000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>246427</v>
+      </c>
+      <c r="D442" t="n">
+        <v>280404</v>
+      </c>
+      <c r="E442" t="n">
+        <v>259332</v>
+      </c>
+      <c r="F442" t="n">
+        <v>247014</v>
+      </c>
+      <c r="G442" t="n">
+        <v>262250</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.6822435901547856</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>0.6822435901547856</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>277500</v>
+      </c>
+      <c r="C443" t="n">
+        <v>428459</v>
+      </c>
+      <c r="D443" t="n">
+        <v>279578</v>
+      </c>
+      <c r="E443" t="n">
+        <v>258304</v>
+      </c>
+      <c r="F443" t="n">
+        <v>257586</v>
+      </c>
+      <c r="G443" t="n">
+        <v>265156</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.7008845810908764</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>0.7008845810908764</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>278000</v>
+      </c>
+      <c r="C444" t="n">
+        <v>483403</v>
+      </c>
+      <c r="D444" t="n">
+        <v>279513</v>
+      </c>
+      <c r="E444" t="n">
+        <v>258966</v>
+      </c>
+      <c r="F444" t="n">
+        <v>265840</v>
+      </c>
+      <c r="G444" t="n">
+        <v>268106</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.7198078169000532</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성생명_일별_기준주가.xlsx
+++ b/data/삼성생명_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>0.7198078169000532</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>270500</v>
+      </c>
+      <c r="C445" t="n">
+        <v>441200</v>
+      </c>
+      <c r="D445" t="n">
+        <v>279188</v>
+      </c>
+      <c r="E445" t="n">
+        <v>258797</v>
+      </c>
+      <c r="F445" t="n">
+        <v>269155</v>
+      </c>
+      <c r="G445" t="n">
+        <v>269046</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.7258375937341639</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
